--- a/data/trans_dic/P25A$otro-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,53</t>
+          <t>0,76; 7,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,33</t>
+          <t>0,51; 4,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 13,18</t>
+          <t>2,57; 11,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 24,5</t>
+          <t>4,56; 23,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,32</t>
+          <t>1,31; 11,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 20,51</t>
+          <t>3,36; 20,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,89</t>
+          <t>1,85; 8,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,71</t>
+          <t>0,79; 4,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,4</t>
+          <t>4,17; 12,1</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,2</t>
+          <t>1,06; 5,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,51</t>
+          <t>0,41; 3,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 15,01</t>
+          <t>5,99; 14,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 27,1</t>
+          <t>7,93; 25,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 15,6</t>
+          <t>3,93; 17,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 15,6</t>
+          <t>4,17; 15,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,94</t>
+          <t>3,98; 10,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,67</t>
+          <t>1,53; 5,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,21</t>
+          <t>6,46; 13,34</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,55</t>
+          <t>0,54; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,68</t>
+          <t>3,12; 12,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 24,64</t>
+          <t>4,4; 24,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,86</t>
+          <t>1,9; 10,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 26,46</t>
+          <t>9,02; 27,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,46</t>
+          <t>1,61; 7,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,46</t>
+          <t>1,43; 5,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 14,87</t>
+          <t>6,34; 14,89</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,77</t>
+          <t>0,49; 6,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,32</t>
+          <t>1,44; 7,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,53</t>
+          <t>9,23; 19,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,21</t>
+          <t>2,18; 14,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,24</t>
+          <t>0,85; 7,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 23,28</t>
+          <t>9,14; 23,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,24</t>
+          <t>1,74; 6,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,45</t>
+          <t>1,78; 6,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 19,13</t>
+          <t>10,2; 18,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,85</t>
+          <t>1,29; 3,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,57</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,09</t>
+          <t>7,13; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,29</t>
+          <t>7,57; 15,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,42</t>
+          <t>3,17; 7,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,24</t>
+          <t>9,39; 16,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,47</t>
+          <t>3,45; 6,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,91</t>
+          <t>8,8; 12,82</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>982; 8455</t>
+          <t>980; 10037</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>919; 8175</t>
+          <t>954; 9025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3229; 15578</t>
+          <t>3040; 13734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1072; 10119</t>
+          <t>1884; 9830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>955; 8878</t>
+          <t>945; 8021</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1806; 11037</t>
+          <t>1809; 11266</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3915; 15176</t>
+          <t>3158; 15019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2852; 12277</t>
+          <t>2047; 12338</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6448; 19607</t>
+          <t>7174; 20815</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1884; 11583</t>
+          <t>1980; 11136</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1027; 8729</t>
+          <t>1016; 8591</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10976; 26599</t>
+          <t>10611; 26150</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6374; 20849</t>
+          <t>6105; 19857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3282; 15335</t>
+          <t>3869; 17069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3613; 13466</t>
+          <t>3603; 13475</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10085; 26229</t>
+          <t>10508; 28121</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5320; 19684</t>
+          <t>5316; 19957</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16631; 34811</t>
+          <t>17017; 35160</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6587</t>
+          <t>0; 6842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>911; 7844</t>
+          <t>937; 8268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4173; 15597</t>
+          <t>4163; 16685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1747; 9779</t>
+          <t>1748; 9585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1996; 11209</t>
+          <t>1961; 10667</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6963; 19728</t>
+          <t>6729; 20280</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2870; 12982</t>
+          <t>2806; 12980</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3924; 15052</t>
+          <t>3951; 15424</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13145; 30946</t>
+          <t>13184; 30985</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>844; 10042</t>
+          <t>859; 12045</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3778; 17163</t>
+          <t>2974; 16341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15649; 34467</t>
+          <t>16286; 34638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2014; 12262</t>
+          <t>2020; 13425</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>926; 8175</t>
+          <t>957; 8149</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10780; 28191</t>
+          <t>11075; 28868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4946; 19307</t>
+          <t>4646; 18231</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5124; 20610</t>
+          <t>5696; 20526</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30419; 56922</t>
+          <t>30368; 56030</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8406; 24022</t>
+          <t>8086; 24256</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10634; 29115</t>
+          <t>9690; 27799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43893; 73216</t>
+          <t>43197; 71994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18170; 38337</t>
+          <t>18981; 39836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11097; 28684</t>
+          <t>12242; 29632</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33090; 57877</t>
+          <t>31537; 56648</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30420; 56623</t>
+          <t>30197; 55524</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25667; 51431</t>
+          <t>25339; 49613</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81630; 121487</t>
+          <t>82874; 120653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$otro-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,75</t>
+          <t>0,75; 6,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,78</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,62</t>
+          <t>2,67; 11,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 23,8</t>
+          <t>4,43; 24,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,13</t>
+          <t>1,32; 11,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 20,94</t>
+          <t>3,44; 21,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,8</t>
+          <t>2,3; 8,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,73</t>
+          <t>0,81; 4,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,1</t>
+          <t>3,94; 12,49</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,96</t>
+          <t>1,02; 5,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,45</t>
+          <t>0,41; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 14,75</t>
+          <t>5,79; 14,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 25,81</t>
+          <t>8,2; 25,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 17,36</t>
+          <t>3,27; 15,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 15,61</t>
+          <t>4,17; 15,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,66</t>
+          <t>3,84; 10,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,75</t>
+          <t>1,56; 5,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,34</t>
+          <t>6,29; 13,62</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,8</t>
+          <t>0,54; 4,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,49</t>
+          <t>3,04; 11,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 24,16</t>
+          <t>4,42; 25,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,34</t>
+          <t>1,9; 10,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 27,2</t>
+          <t>9,06; 28,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,46</t>
+          <t>1,57; 7,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,6</t>
+          <t>1,28; 5,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 14,89</t>
+          <t>6,49; 14,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,92</t>
+          <t>0,49; 5,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,92</t>
+          <t>1,82; 8,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 19,63</t>
+          <t>9,01; 19,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,46</t>
+          <t>2,3; 13,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,21</t>
+          <t>0,83; 7,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 23,84</t>
+          <t>8,31; 22,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,83</t>
+          <t>1,83; 6,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,43</t>
+          <t>1,82; 6,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 18,83</t>
+          <t>10,41; 19,08</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,88</t>
+          <t>1,31; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,89</t>
+          <t>7,27; 12,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>7,47; 15,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,67</t>
+          <t>2,91; 7,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,87</t>
+          <t>9,14; 16,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,34</t>
+          <t>3,52; 6,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,07; 4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,82</t>
+          <t>8,68; 12,7</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>980; 10037</t>
+          <t>975; 8479</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>954; 9025</t>
+          <t>0; 8102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3040; 13734</t>
+          <t>3152; 13908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1884; 9830</t>
+          <t>1830; 10089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>945; 8021</t>
+          <t>953; 8093</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1809; 11266</t>
+          <t>1850; 11495</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3158; 15019</t>
+          <t>3924; 14896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2047; 12338</t>
+          <t>2121; 12774</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7174; 20815</t>
+          <t>6784; 21478</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1980; 11136</t>
+          <t>1913; 10884</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1016; 8591</t>
+          <t>1011; 8657</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10611; 26150</t>
+          <t>10261; 26363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6105; 19857</t>
+          <t>6307; 19586</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3869; 17069</t>
+          <t>3218; 15068</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3603; 13475</t>
+          <t>3599; 13285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10508; 28121</t>
+          <t>10140; 27173</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5316; 19957</t>
+          <t>5412; 20612</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17017; 35160</t>
+          <t>16577; 35910</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6842</t>
+          <t>0; 6920</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>937; 8268</t>
+          <t>926; 7764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4163; 16685</t>
+          <t>4057; 14849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1748; 9585</t>
+          <t>1756; 10152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1961; 10667</t>
+          <t>1958; 11154</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6729; 20280</t>
+          <t>6759; 21165</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2806; 12980</t>
+          <t>2735; 13108</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3951; 15424</t>
+          <t>3534; 14963</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13184; 30985</t>
+          <t>13507; 30543</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>859; 12045</t>
+          <t>854; 10038</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2974; 16341</t>
+          <t>3752; 17346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16286; 34638</t>
+          <t>15901; 35097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2020; 13425</t>
+          <t>2131; 12857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>957; 8149</t>
+          <t>939; 8444</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11075; 28868</t>
+          <t>10059; 27629</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4646; 18231</t>
+          <t>4891; 18055</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5696; 20526</t>
+          <t>5822; 20116</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30368; 56030</t>
+          <t>30982; 56770</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8086; 24256</t>
+          <t>8171; 23471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9690; 27799</t>
+          <t>8965; 27330</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43197; 71994</t>
+          <t>44049; 73170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18981; 39836</t>
+          <t>18728; 38528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12242; 29632</t>
+          <t>11235; 29119</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31537; 56648</t>
+          <t>30698; 57047</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30197; 55524</t>
+          <t>30810; 55759</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25339; 49613</t>
+          <t>24869; 48291</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82874; 120653</t>
+          <t>81718; 119585</t>
         </is>
       </c>
     </row>
